--- a/data/trans_bre/P12_3_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P12_3_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,97</t>
+          <t>0,02; 4,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 8,16</t>
+          <t>1,94; 8,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 11,5</t>
+          <t>4,6; 12,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 11,03</t>
+          <t>3,02; 10,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 63,04</t>
+          <t>0,19; 63,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,87; 67,05</t>
+          <t>11,75; 69,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,62; 99,15</t>
+          <t>30,76; 105,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,81; 72,08</t>
+          <t>15,04; 69,73</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,64</t>
+          <t>1,58; 4,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,38</t>
+          <t>2,74; 6,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,9</t>
+          <t>1,42; 4,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 5,33</t>
+          <t>-0,41; 5,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,72; 165,5</t>
+          <t>37,82; 167,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,96; 116,46</t>
+          <t>38,73; 116,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,26; 98,77</t>
+          <t>21,62; 93,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 83,85</t>
+          <t>-3,33; 87,23</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,82</t>
+          <t>1,55; 7,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 6,03</t>
+          <t>-0,47; 5,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 1,8</t>
+          <t>-3,81; 1,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 1,83</t>
+          <t>-6,39; 1,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,84; 413,21</t>
+          <t>32,88; 407,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 259,4</t>
+          <t>-19,3; 238,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-55,37; 52,09</t>
+          <t>-54,79; 55,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-48,43; 26,64</t>
+          <t>-48,8; 26,57</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,66</t>
+          <t>2,2; 4,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,75</t>
+          <t>3,72; 6,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,77</t>
+          <t>2,91; 5,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,26</t>
+          <t>0,72; 5,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,51; 103,14</t>
+          <t>38,81; 104,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,85; 90,86</t>
+          <t>42,5; 92,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,44; 85,06</t>
+          <t>36,01; 84,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 63,02</t>
+          <t>7,13; 69,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P12_3_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P12_3_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,12</t>
+          <t>8,29</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>47,08%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 4,98</t>
+          <t>-0,19; 4,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 8,27</t>
+          <t>1,99; 8,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 12,28</t>
+          <t>4,29; 11,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 10,71</t>
+          <t>4,24; 11,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 63,87</t>
+          <t>-2,03; 62,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,75; 69,04</t>
+          <t>13,13; 69,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,76; 105,32</t>
+          <t>26,15; 98,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,04; 69,73</t>
+          <t>19,78; 77,73</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,38</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,68</t>
+          <t>1,64; 4,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,52</t>
+          <t>2,66; 6,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,74</t>
+          <t>1,36; 4,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 5,61</t>
+          <t>0,96; 4,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,82; 167,78</t>
+          <t>38,24; 174,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,73; 116,7</t>
+          <t>36,89; 114,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,62; 93,43</t>
+          <t>20,65; 96,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 87,23</t>
+          <t>8,54; 53,46</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-13,58%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,05</t>
+          <t>1,49; 7,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 5,89</t>
+          <t>-0,58; 5,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 1,99</t>
+          <t>-3,6; 1,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 1,77</t>
+          <t>-2,23; 3,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,88; 407,63</t>
+          <t>37,16; 445,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 238,78</t>
+          <t>-17,67; 254,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-54,79; 55,67</t>
+          <t>-53,33; 43,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-48,8; 26,57</t>
+          <t>-23,27; 54,58</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,25</t>
+          <t>4,08</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>38,62%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,7</t>
+          <t>2,29; 4,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,85</t>
+          <t>3,58; 6,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,79</t>
+          <t>2,8; 5,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,62</t>
+          <t>2,55; 5,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,81; 104,09</t>
+          <t>41,28; 107,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,5; 92,34</t>
+          <t>40,87; 92,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,01; 84,89</t>
+          <t>35,28; 82,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,13; 69,03</t>
+          <t>21,99; 57,29</t>
         </is>
       </c>
     </row>
